--- a/data/trans_camb/P43B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P43B-Clase-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>8,72</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,12</t>
+          <t>8,72</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 5,56</t>
+          <t>-16,96; 6,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 20,35</t>
+          <t>-1,9; 19,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 5,56</t>
+          <t>-16,96; 6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 20,35</t>
+          <t>-1,9; 19,01</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 19,63</t>
+          <t>-39,21; 22,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 72,23</t>
+          <t>-4,18; 66,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 19,63</t>
+          <t>-39,21; 22,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 72,23</t>
+          <t>-4,18; 66,65</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,63</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 2,82</t>
+          <t>-19,91; 2,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 11,24</t>
+          <t>-12,21; 10,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 2,82</t>
+          <t>-19,91; 2,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 11,24</t>
+          <t>-12,21; 10,4</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,34%</t>
+          <t>-1,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,34%</t>
+          <t>-1,77%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 11,6</t>
+          <t>-47,63; 8,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 39,24</t>
+          <t>-27,13; 38,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 11,6</t>
+          <t>-47,63; 8,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 39,24</t>
+          <t>-27,13; 38,25</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 7,62</t>
+          <t>-11,31; 8,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 9,67</t>
+          <t>-10,31; 7,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 7,62</t>
+          <t>-11,31; 8,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 9,67</t>
+          <t>-10,31; 7,94</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-3,36%</t>
+          <t>-6,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,36%</t>
+          <t>-6,51%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 67,88</t>
+          <t>-55,31; 80,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 85,77</t>
+          <t>-50,62; 70,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 67,88</t>
+          <t>-55,31; 80,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 85,77</t>
+          <t>-50,62; 70,86</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>-0,56</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 1,5</t>
+          <t>-9,85; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 0,79</t>
+          <t>-6,02; 4,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 1,5</t>
+          <t>-9,85; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 0,79</t>
+          <t>-6,02; 4,33</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-46,87%</t>
+          <t>-3,96%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-46,87%</t>
+          <t>-3,96%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 14,2</t>
+          <t>-56,18; 16,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,59; 7,75</t>
+          <t>-34,58; 40,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 14,2</t>
+          <t>-56,18; 16,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,59; 7,75</t>
+          <t>-34,58; 40,5</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,04</t>
+          <t>-7,25; -0,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,03</t>
+          <t>-5,61; 1,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,04</t>
+          <t>-7,25; -0,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,03</t>
+          <t>-5,61; 1,75</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-32,23%</t>
+          <t>-23,77%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-32,23%</t>
+          <t>-23,77%</t>
         </is>
       </c>
     </row>
@@ -1121,29 +1121,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 1,02</t>
+          <t>-69,18; -0,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,85; 16,25</t>
+          <t>-53,35; 28,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 1,02</t>
+          <t>-69,18; -0,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-63,85; 16,25</t>
+          <t>-53,35; 28,8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,46</t>
+          <t>-2,75; 4,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,66</t>
+          <t>-3,5; 3,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,46</t>
+          <t>-2,75; 4,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,66</t>
+          <t>-3,5; 3,69</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 74,44</t>
+          <t>-28,97; 64,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 56,82</t>
+          <t>-35,81; 54,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 74,44</t>
+          <t>-28,97; 64,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 56,82</t>
+          <t>-35,81; 54,82</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>3,74</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,69</t>
+          <t>-4,72; 0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,25</t>
+          <t>1,35; 6,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,69</t>
+          <t>-4,72; 0,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 4,25</t>
+          <t>1,35; 6,09</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 5,55</t>
+          <t>-29,29; 3,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 31,03</t>
+          <t>8,3; 47,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 5,55</t>
+          <t>-29,29; 3,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 31,03</t>
+          <t>8,3; 47,36</t>
         </is>
       </c>
     </row>
